--- a/course-design-2/outputs/tables/ch5/25_final_interpretation_audit.xlsx
+++ b/course-design-2/outputs/tables/ch5/25_final_interpretation_audit.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_公司认证统计" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_公司标签统计" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Stage13修正前后" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_技能SHAP旧口径" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_技能SHAP_presence口径" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_技能SHAP旧统计范围" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_技能SHAP_presence 统计方式" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_关键结果一致性" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_全阶段门禁" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_测试结果" sheetId="9" state="visible" r:id="rId9"/>

--- a/course-design-2/outputs/tables/ch5/25_final_interpretation_audit.xlsx
+++ b/course-design-2/outputs/tables/ch5/25_final_interpretation_audit.xlsx
@@ -2972,7 +2972,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>频率口径</t>
+          <t>频率统计方式</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -3007,7 +3007,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3045,7 +3044,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3083,7 +3081,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3121,7 +3118,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3159,7 +3155,6 @@
           <t>正向（提高预测薪资）</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3197,7 +3192,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3235,7 +3229,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3273,7 +3266,6 @@
           <t>正向（提高预测薪资）</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3311,7 +3303,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3349,7 +3340,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3387,7 +3377,6 @@
           <t>正向（提高预测薪资）</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3425,7 +3414,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3463,7 +3451,6 @@
           <t>正向（提高预测薪资）</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3501,7 +3488,6 @@
           <t>正向（提高预测薪资）</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3539,7 +3525,6 @@
           <t>正向（提高预测薪资）</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3577,7 +3562,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3615,7 +3599,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3653,7 +3636,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3691,7 +3673,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3729,7 +3710,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3767,7 +3747,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3805,7 +3784,6 @@
           <t>正向（提高预测薪资）</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3843,7 +3821,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3881,7 +3858,6 @@
           <t>正向（提高预测薪资）</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3919,7 +3895,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3957,7 +3932,6 @@
           <t>正向（提高预测薪资）</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -3995,7 +3969,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -4033,7 +4006,6 @@
           <t>正向（提高预测薪资）</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -4071,7 +4043,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -4109,7 +4080,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -4147,7 +4117,6 @@
           <t>正向（提高预测薪资）</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -4185,7 +4154,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -4223,7 +4191,6 @@
           <t>正向（提高预测薪资）</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -4261,7 +4228,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -4299,7 +4265,6 @@
           <t>正向（提高预测薪资）</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -4337,7 +4302,6 @@
           <t>正向（提高预测薪资）</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -4375,7 +4339,6 @@
           <t>正向（提高预测薪资）</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -4413,7 +4376,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -4451,7 +4413,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -4489,7 +4450,6 @@
           <t>负向（降低预测薪资）</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -4527,7 +4487,6 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -4565,7 +4524,6 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -4603,7 +4561,6 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
@@ -4641,7 +4598,6 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Stage 12 建模样本 14,883 个岗位（ALL_USABLE 技能口径）</t>
